--- a/docs/qa/upload-templates/product_master_upload_template.xlsx
+++ b/docs/qa/upload-templates/product_master_upload_template.xlsx
@@ -133,27 +133,52 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Required unique SKU</t>
+        <t>Unique SKU / item code (required)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Required product name EN</t>
+        <t>Family/group e.g. DT, PT, RM-CU (required)</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>finished|semi|raw</t>
+        <t>finished|semi|raw (required)</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>EA, KG, etc.</t>
+        <t>Short display name (required)</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
+        <t>Full commercial/technical name (required)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Unit of measure: EA, KG, M, L (required)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Default warehouse/bin e.g. WH-FG (required)</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
         <t>Optional Arabic name</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>A|B|C optional</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>true|false</t>
       </text>
     </comment>
   </commentList>
@@ -449,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +485,82 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>product_group</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>product_type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>short_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>uom</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_storage_location</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>name_ar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>standard_cost</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>safety_stock</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>reorder_point</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>lead_time_days</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>abc_class</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>weight_kg</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>hs_code</t>
         </is>
       </c>
     </row>
@@ -487,7 +572,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dist Transform 100kVA</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -497,12 +582,62 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>DT100</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Distribution Transformer 100kVA Oil-Immersed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>محول توزيع 100</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>WH-FG</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>محول توزيع 100 ك.ف.أ</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>680</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>850421</t>
         </is>
       </c>
     </row>
@@ -514,7 +649,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dist Transform 250kVA</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -524,12 +659,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>DT250</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Distribution Transformer 250kVA Oil-Immersed</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>محول توزيع 250</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>WH-FG</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>محول توزيع 250 ك.ف.أ</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>85000</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>28</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>850421</t>
         </is>
       </c>
     </row>
@@ -541,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Copper wire 25mm</t>
+          <t>RM-CU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -551,14 +736,137 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CuWire25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Copper Winding Wire 25mm2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>سلك نحاس</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>WH-RM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>سلك نحاس 25 مم</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>740819</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SF-CORE100</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>semi</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Core100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Magnetic Core Assembly 100kVA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>WH-WIP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>قلب مغناطيسي 100</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>8200</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
